--- a/покупки/себестоимость.xlsx
+++ b/покупки/себестоимость.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\покупки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720E682B-0F9B-451A-B979-0DA3EDA3E841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91246324-B3D4-4B18-8814-2BF2E3786C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="01.07.2025" sheetId="4" r:id="rId5"/>
     <sheet name="25.07.2025" sheetId="5" r:id="rId6"/>
     <sheet name="Лист3" sheetId="6" r:id="rId7"/>
+    <sheet name="Лист5" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
   <si>
     <t>Pet Film, 60cm*100m</t>
   </si>
@@ -241,6 +242,9 @@
   </si>
   <si>
     <t>Пленка, 60cm*100m</t>
+  </si>
+  <si>
+    <t>Order Max Uzkikh 25.03.2026</t>
   </si>
 </sst>
 </file>
@@ -2345,4 +2349,140 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{897D6E71-F267-41EE-82E4-DF1396A99E8B}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7">
+        <v>36</v>
+      </c>
+      <c r="C2" s="8">
+        <v>29</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" ref="D2:D4" si="0">B2*C2</f>
+        <v>1044</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1.281E-2</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" ref="F2:F3" si="1">B2*E2</f>
+        <v>0.46116000000000001</v>
+      </c>
+      <c r="G2" s="7">
+        <v>7.35</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" ref="H2:H3" si="2">B2*G2</f>
+        <v>264.59999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="7">
+        <v>120</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3.0079999999999998E-3</v>
+      </c>
+      <c r="F3" s="7">
+        <f t="shared" si="1"/>
+        <v>0.36096</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="10">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7">
+        <f>SUM(D2:D4)</f>
+        <v>1674</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7">
+        <f>SUM(F2:F3)</f>
+        <v>0.82211999999999996</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <f>SUM(H2:H3)</f>
+        <v>396.59999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/покупки/себестоимость.xlsx
+++ b/покупки/себестоимость.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\покупки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91246324-B3D4-4B18-8814-2BF2E3786C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59A4587-C43F-4871-B70E-208BEE1A0687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Лист3" sheetId="6" r:id="rId7"/>
     <sheet name="Лист5" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2360,7 +2360,7 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>63</v>
       </c>

--- a/покупки/себестоимость.xlsx
+++ b/покупки/себестоимость.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\покупки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59A4587-C43F-4871-B70E-208BEE1A0687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979A6614-03EB-40E2-89C9-1C6B73D54947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="25.07.2025" sheetId="5" r:id="rId6"/>
     <sheet name="Лист3" sheetId="6" r:id="rId7"/>
     <sheet name="Лист5" sheetId="8" r:id="rId8"/>
+    <sheet name="21.05.2026" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="65">
   <si>
     <t>Pet Film, 60cm*100m</t>
   </si>
@@ -245,6 +246,9 @@
   </si>
   <si>
     <t>Order Max Uzkikh 25.03.2026</t>
+  </si>
+  <si>
+    <t>Order Max Uzkikh 21.05.2026</t>
   </si>
 </sst>
 </file>
@@ -2485,4 +2489,93 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E3F2A1-31CB-45B2-9B57-BD445D83FEC0}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="7">
+        <v>260</v>
+      </c>
+      <c r="C2" s="8">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" ref="D2" si="0">B2*C2</f>
+        <v>1300</v>
+      </c>
+      <c r="E2" s="7">
+        <v>3.0079999999999998E-3</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" ref="F2" si="1">B2*E2</f>
+        <v>0.78208</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" ref="H2" si="2">B2*G2</f>
+        <v>327.60000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7">
+        <f>SUM(D2:D2)</f>
+        <v>1300</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7">
+        <f>SUM(F2:F2)</f>
+        <v>0.78208</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7">
+        <f>SUM(H2:H2)</f>
+        <v>327.60000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>